--- a/hss-f25.xlsx
+++ b/hss-f25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Fall/Report Generation/AQA Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6388759-B9EA-4774-990E-A2ABD5AB614E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93CAAFD4-B88F-4E38-9489-D3D70E7F4C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4F6B00C-EE64-42AC-92A2-B5759173BE86}"/>
+    <workbookView xWindow="-38520" yWindow="-4680" windowWidth="38640" windowHeight="21120" xr2:uid="{91066042-D9DC-45D9-863D-57BA61CD55F4}"/>
   </bookViews>
   <sheets>
     <sheet name="hss-f25" sheetId="1" r:id="rId1"/>
@@ -1573,7 +1573,7 @@
     <t>Report prepared by HKUST</t>
   </si>
   <si>
-    <t>30 January 2026</t>
+    <t>28 February 2026</t>
   </si>
 </sst>
 </file>
@@ -2452,7 +2452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDF0666E-0A8B-4659-AA80-9AE45488CD8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F22A1-55E4-4B47-9D29-62FDE303D9D7}">
   <dimension ref="A1:AA362"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25608,285 +25608,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064FBF1EC94D9E9419E928C7F04731A98" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5d1fc6aea0bdb544d42f3777360a695">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="307c76f0-d205-4835-9aae-d70c69349486" xmlns:ns3="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91955e799b8657f65baef53610b4215d" ns2:_="" ns3:_="">
-    <xsd:import namespace="307c76f0-d205-4835-9aae-d70c69349486"/>
-    <xsd:import namespace="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="307c76f0-d205-4835-9aae-d70c69349486" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="10" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f9659908-461d-4310-9e2e-8d0890ed1ef9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{2c007c70-c01f-4ffe-952d-2d46dec0e54b}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="c1544048-3019-4d62-a7f3-2ad0cae9f9e9">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="307c76f0-d205-4835-9aae-d70c69349486">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AF98C4A-2520-487F-9CE9-DA9C3F3483C8}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13BB001B-D64B-4AC5-AE1E-EA32E5051FCB}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4AED68-DC74-4C7E-9DC4-9892D0B3E9DE}"/>
 </file>